--- a/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_decimal_place_correction.xlsx
+++ b/results/05_transient_transcription_output/209/209_196810_SF.JPG_stage_decimal_place_correction.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FF9933"/>
-        <bgColor rgb="00FF9933"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="9">
@@ -107,7 +101,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment textRotation="90"/>
@@ -122,9 +116,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -744,8 +735,8 @@
       <c r="E4" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F4" s="8" t="n">
-        <v>124.2</v>
+      <c r="F4" s="3" t="n">
+        <v>24.2</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>14</v>
@@ -765,7 +756,7 @@
       <c r="L4" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="M4" s="8" t="n">
+      <c r="M4" s="3" t="n">
         <v>16.2</v>
       </c>
       <c r="N4" s="3" t="n">
@@ -795,7 +786,7 @@
       <c r="V4" s="3" t="n">
         <v>27.7</v>
       </c>
-      <c r="W4" s="8" t="n">
+      <c r="W4" s="3" t="n">
         <v>24</v>
       </c>
       <c r="X4" s="3" t="inlineStr"/>
@@ -830,14 +821,14 @@
         <v>5.7</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>8.6</v>
+        <v>1.6</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>0.3</v>
       </c>
       <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="n">
-        <v>25.4</v>
+        <v>25.8</v>
       </c>
       <c r="L5" s="3" t="n">
         <v>19.1</v>
@@ -860,7 +851,7 @@
       <c r="R5" s="3" t="n">
         <v>19.1</v>
       </c>
-      <c r="S5" s="8" t="n">
+      <c r="S5" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="T5" s="3" t="n">
@@ -906,7 +897,7 @@
       <c r="E6" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="F6" s="3" t="n">
         <v>25.6</v>
       </c>
       <c r="G6" s="3" t="n">
@@ -921,8 +912,8 @@
       <c r="J6" s="3" t="n">
         <v>3.6</v>
       </c>
-      <c r="K6" s="8" t="n">
-        <v>0.6</v>
+      <c r="K6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>20.3</v>
@@ -995,7 +986,7 @@
       <c r="G7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="H7" s="8" t="n">
+      <c r="H7" s="3" t="n">
         <v>14.8</v>
       </c>
       <c r="I7" s="3" t="n">
@@ -1005,7 +996,7 @@
         <v>4.9</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>17.3</v>
@@ -1013,11 +1004,11 @@
       <c r="M7" s="3" t="n">
         <v>16</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="N7" s="3" t="n">
         <v>17.3</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>872.6</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>2.5</v>
@@ -1032,7 +1023,7 @@
         <v>24.6</v>
       </c>
       <c r="T7" s="3" t="n">
-        <v>152.1</v>
+        <v>52.1</v>
       </c>
       <c r="U7" s="3" t="n">
         <v>22.6</v>
@@ -1066,9 +1057,9 @@
         </is>
       </c>
       <c r="C8" s="3" t="n">
-        <v>29.7</v>
-      </c>
-      <c r="D8" s="8" t="n">
+        <v>297.2</v>
+      </c>
+      <c r="D8" s="3" t="n">
         <v>32.6</v>
       </c>
       <c r="E8" s="3" t="n">
@@ -1077,7 +1068,7 @@
       <c r="F8" s="3" t="n">
         <v>26.2</v>
       </c>
-      <c r="G8" s="8" t="n">
+      <c r="G8" s="3" t="n">
         <v>12.8</v>
       </c>
       <c r="H8" s="3" t="n">
@@ -1132,7 +1123,7 @@
         <v>27.8</v>
       </c>
       <c r="Y8" s="3" t="n">
-        <v>175.2</v>
+        <v>75.2</v>
       </c>
       <c r="Z8" s="3" t="n">
         <v>27</v>
@@ -1154,13 +1145,13 @@
         <v>166.6</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>852.6</v>
+        <v>152.6</v>
       </c>
       <c r="E9" s="3" t="n">
         <v>92.5</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>822.5</v>
+        <v>122.5</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>6</v>
@@ -1187,7 +1178,7 @@
         <v>96.3</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>440.9</v>
+        <v>22.2</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>12.9</v>
@@ -1196,7 +1187,7 @@
         <v>138.8</v>
       </c>
       <c r="R9" s="3" t="n">
-        <v>1617.3</v>
+        <v>117.3</v>
       </c>
       <c r="S9" s="3" t="n">
         <v>131.9</v>
@@ -1263,12 +1254,12 @@
         <v>0.1</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="M10" s="8" t="n">
-        <v>87.59999999999999</v>
-      </c>
-      <c r="N10" s="8" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="M10" s="3" t="n">
+        <v>17.6</v>
+      </c>
+      <c r="N10" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="O10" s="3" t="n">
@@ -1280,7 +1271,7 @@
       <c r="Q10" s="3" t="n">
         <v>27.8</v>
       </c>
-      <c r="R10" s="8" t="n">
+      <c r="R10" s="3" t="n">
         <v>23.5</v>
       </c>
       <c r="S10" s="3" t="n">
@@ -1329,7 +1320,7 @@
       <c r="E11" s="3" t="n">
         <v>19.9</v>
       </c>
-      <c r="F11" s="8" t="n">
+      <c r="F11" s="3" t="n">
         <v>24.3</v>
       </c>
       <c r="G11" s="3" t="n">
@@ -1369,7 +1360,7 @@
         <v>25.8</v>
       </c>
       <c r="S11" s="3" t="n">
-        <v>81.90000000000001</v>
+        <v>31.9</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>850.1</v>
@@ -1408,7 +1399,7 @@
       <c r="C12" s="3" t="n">
         <v>38.3</v>
       </c>
-      <c r="D12" s="8" t="n">
+      <c r="D12" s="3" t="n">
         <v>28.1</v>
       </c>
       <c r="E12" s="3" t="n">
@@ -1421,7 +1412,7 @@
         <v>8.5</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>2.9</v>
@@ -1445,7 +1436,7 @@
         <v>88.40000000000001</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>12.7</v>
+        <v>2.7</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>27.2</v>
@@ -1468,11 +1459,11 @@
       <c r="W12" s="3" t="n">
         <v>24.4</v>
       </c>
-      <c r="X12" s="8" t="n">
+      <c r="X12" s="3" t="n">
         <v>30.4</v>
       </c>
       <c r="Y12" s="3" t="n">
-        <v>1197.7</v>
+        <v>97.7</v>
       </c>
       <c r="Z12" s="3" t="n">
         <v>0.7</v>
@@ -1491,7 +1482,7 @@
         </is>
       </c>
       <c r="C13" s="3" t="n">
-        <v>235.6</v>
+        <v>35.6</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>31.1</v>
@@ -1576,7 +1567,7 @@
         </is>
       </c>
       <c r="C14" s="3" t="n">
-        <v>37.4</v>
+        <v>374</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>32.5</v>
@@ -1605,7 +1596,7 @@
       <c r="L14" s="3" t="n">
         <v>19.8</v>
       </c>
-      <c r="M14" s="8" t="n">
+      <c r="M14" s="3" t="n">
         <v>18.7</v>
       </c>
       <c r="N14" s="3" t="n">
@@ -1629,7 +1620,7 @@
       <c r="T14" s="3" t="n">
         <v>50.9</v>
       </c>
-      <c r="U14" s="8" t="n">
+      <c r="U14" s="3" t="n">
         <v>21.6</v>
       </c>
       <c r="V14" s="3" t="n">
@@ -1638,7 +1629,7 @@
       <c r="W14" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X14" s="8" t="n">
+      <c r="X14" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="Y14" s="3" t="n">
@@ -1661,13 +1652,13 @@
         </is>
       </c>
       <c r="C15" s="3" t="n">
-        <v>143.3</v>
+        <v>43.3</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>29.5</v>
       </c>
-      <c r="E15" s="8" t="n">
-        <v>2.8</v>
+      <c r="E15" s="3" t="n">
+        <v>20.2</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>24.9</v>
@@ -1690,8 +1681,8 @@
       <c r="L15" s="3" t="n">
         <v>20.4</v>
       </c>
-      <c r="M15" s="8" t="n">
-        <v>29.1</v>
+      <c r="M15" s="3" t="n">
+        <v>19.1</v>
       </c>
       <c r="N15" s="3" t="n">
         <v>21.3</v>
@@ -1717,13 +1708,13 @@
       <c r="U15" s="3" t="n">
         <v>14.1</v>
       </c>
-      <c r="V15" s="8" t="n">
+      <c r="V15" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="W15" s="3" t="n">
         <v>21.1</v>
       </c>
-      <c r="X15" s="8" t="n">
+      <c r="X15" s="3" t="n">
         <v>22.8</v>
       </c>
       <c r="Y15" s="3" t="n">
@@ -1746,7 +1737,7 @@
         </is>
       </c>
       <c r="C16" s="3" t="n">
-        <v>1992.8</v>
+        <v>1992.6</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>149.9</v>
@@ -1761,20 +1752,20 @@
         <v>508.1</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>11.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>115.8</v>
+        <v>15.8</v>
       </c>
       <c r="K16" s="3" t="inlineStr"/>
       <c r="L16" s="3" t="n">
         <v>1.9</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>194.6</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="N16" s="3" t="n">
         <v>105.2</v>
@@ -1792,7 +1783,7 @@
         <v>123</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>1042.5</v>
+        <v>142.5</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>368.7</v>
@@ -1829,7 +1820,7 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>399.8</v>
+        <v>39.8</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>30</v>
@@ -1841,10 +1832,10 @@
         <v>24.9</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>28.1</v>
+        <v>18.1</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>2.2</v>
@@ -1852,10 +1843,10 @@
       <c r="J17" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="K17" s="8" t="n">
-        <v>11551.5</v>
-      </c>
-      <c r="L17" s="8" t="n">
+      <c r="K17" s="3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L17" s="3" t="n">
         <v>20.2</v>
       </c>
       <c r="M17" s="3" t="n">
@@ -1880,7 +1871,7 @@
         <v>28.5</v>
       </c>
       <c r="T17" s="3" t="n">
-        <v>173.7</v>
+        <v>73.7</v>
       </c>
       <c r="U17" s="3" t="n">
         <v>10.6</v>
@@ -1926,13 +1917,13 @@
         <v>24.9</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>11.3</v>
+        <v>11.8</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>14.2</v>
+        <v>17.2</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>13.5</v>
+        <v>3.5</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>4</v>
@@ -1944,10 +1935,10 @@
         <v>19.2</v>
       </c>
       <c r="M18" s="3" t="n">
-        <v>20.8</v>
+        <v>17.7</v>
       </c>
       <c r="N18" s="3" t="n">
-        <v>13.3</v>
+        <v>19.3</v>
       </c>
       <c r="O18" s="3" t="n">
         <v>87</v>
@@ -1974,7 +1965,7 @@
         <v>26</v>
       </c>
       <c r="W18" s="3" t="n">
-        <v>25.6</v>
+        <v>25</v>
       </c>
       <c r="X18" s="3" t="n">
         <v>31</v>
@@ -1999,7 +1990,7 @@
         </is>
       </c>
       <c r="C19" s="3" t="n">
-        <v>2223.4</v>
+        <v>423.4</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>32.5</v>
@@ -2011,10 +2002,10 @@
         <v>25.5</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>18.4</v>
+        <v>1.4</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>11.6</v>
+        <v>1.6</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>2.6</v>
@@ -2028,7 +2019,7 @@
       <c r="L19" s="3" t="n">
         <v>19.6</v>
       </c>
-      <c r="M19" s="8" t="n">
+      <c r="M19" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="N19" s="3" t="n">
@@ -2099,16 +2090,16 @@
         <v>7.4</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>1.2</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>24.4</v>
+        <v>24</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>20</v>
@@ -2128,8 +2119,8 @@
       <c r="Q20" s="3" t="n">
         <v>25.5</v>
       </c>
-      <c r="R20" s="8" t="n">
-        <v>241.5</v>
+      <c r="R20" s="3" t="n">
+        <v>221.5</v>
       </c>
       <c r="S20" s="3" t="n">
         <v>23.1</v>
@@ -2193,9 +2184,9 @@
         <v>3.4</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="L21" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L21" s="3" t="n">
         <v>18.8</v>
       </c>
       <c r="M21" s="3" t="n">
@@ -2238,7 +2229,7 @@
         <v>85</v>
       </c>
       <c r="Z21" s="3" t="n">
-        <v>14.5</v>
+        <v>4.5</v>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -2254,18 +2245,18 @@
         </is>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2374.6</v>
-      </c>
-      <c r="D22" s="8" t="n">
+        <v>374</v>
+      </c>
+      <c r="D22" s="3" t="n">
         <v>31.8</v>
       </c>
       <c r="E22" s="3" t="n">
         <v>17.2</v>
       </c>
-      <c r="F22" s="8" t="n">
-        <v>247.5</v>
-      </c>
-      <c r="G22" s="8" t="n">
+      <c r="F22" s="3" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="G22" s="3" t="n">
         <v>14.6</v>
       </c>
       <c r="H22" s="3" t="n">
@@ -2283,8 +2274,8 @@
       <c r="L22" s="3" t="n">
         <v>17.6</v>
       </c>
-      <c r="M22" s="8" t="n">
-        <v>26.2</v>
+      <c r="M22" s="3" t="n">
+        <v>16.2</v>
       </c>
       <c r="N22" s="3" t="n">
         <v>17.5</v>
@@ -2305,12 +2296,12 @@
         <v>24.2</v>
       </c>
       <c r="T22" s="3" t="n">
-        <v>256.4</v>
+        <v>56.4</v>
       </c>
       <c r="U22" s="3" t="n">
         <v>18.7</v>
       </c>
-      <c r="V22" s="8" t="n">
+      <c r="V22" s="3" t="n">
         <v>21.2</v>
       </c>
       <c r="W22" s="3" t="n">
@@ -2339,7 +2330,7 @@
         </is>
       </c>
       <c r="C23" s="3" t="n">
-        <v>192.5</v>
+        <v>1925.5</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>153.1</v>
@@ -2351,19 +2342,19 @@
         <v>123</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>60.5</v>
+        <v>60.3</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>85.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>11.6</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>25.5</v>
+        <v>15.5</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>49.5</v>
+        <v>49.2</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>95.2</v>
@@ -2378,7 +2369,7 @@
         <v>437.2</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>113.7</v>
+        <v>13.7</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>146.2</v>
@@ -2390,7 +2381,7 @@
         <v>119</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>2895.2</v>
+        <v>295.2</v>
       </c>
       <c r="U23" s="3" t="n">
         <v>85.40000000000001</v>
@@ -2408,7 +2399,7 @@
         <v>411</v>
       </c>
       <c r="Z23" s="3" t="n">
-        <v>0.8</v>
+        <v>27.1</v>
       </c>
       <c r="AA23" s="3" t="inlineStr">
         <is>
@@ -2424,7 +2415,7 @@
         </is>
       </c>
       <c r="C24" s="3" t="n">
-        <v>1398.5</v>
+        <v>38.5</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>30.6</v>
@@ -2438,8 +2429,8 @@
       <c r="G24" s="3" t="n">
         <v>12</v>
       </c>
-      <c r="H24" s="8" t="n">
-        <v>67.59999999999999</v>
+      <c r="H24" s="3" t="n">
+        <v>17.2</v>
       </c>
       <c r="I24" s="3" t="n">
         <v>2.3</v>
@@ -2448,7 +2439,7 @@
         <v>3.1</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>19</v>
@@ -2457,7 +2448,7 @@
         <v>17.6</v>
       </c>
       <c r="N24" s="3" t="n">
-        <v>12.3</v>
+        <v>19.3</v>
       </c>
       <c r="O24" s="3" t="n">
         <v>87.40000000000001</v>
@@ -2478,7 +2469,7 @@
         <v>59</v>
       </c>
       <c r="U24" s="3" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="V24" s="3" t="n">
         <v>24.4</v>
@@ -2509,15 +2500,15 @@
         </is>
       </c>
       <c r="C25" s="3" t="n">
-        <v>2374</v>
+        <v>374</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>32.1</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F25" s="8" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="F25" s="3" t="n">
         <v>25.7</v>
       </c>
       <c r="G25" s="3" t="n">
@@ -2533,7 +2524,7 @@
         <v>3.6</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>19.5</v>
@@ -2548,7 +2539,7 @@
         <v>90</v>
       </c>
       <c r="P25" s="3" t="n">
-        <v>18.2</v>
+        <v>2.2</v>
       </c>
       <c r="Q25" s="3" t="n">
         <v>31.3</v>
@@ -2557,7 +2548,7 @@
         <v>24.3</v>
       </c>
       <c r="S25" s="3" t="n">
-        <v>22.9</v>
+        <v>25.9</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>56.9</v>
@@ -2571,14 +2562,14 @@
       <c r="W25" s="3" t="n">
         <v>20.9</v>
       </c>
-      <c r="X25" s="8" t="n">
+      <c r="X25" s="3" t="n">
         <v>22.6</v>
       </c>
       <c r="Y25" s="3" t="n">
-        <v>174.8</v>
+        <v>74.8</v>
       </c>
       <c r="Z25" s="3" t="n">
-        <v>17.2</v>
+        <v>7.2</v>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -2609,7 +2600,7 @@
         <v>12.2</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>1.9</v>
@@ -2648,7 +2639,7 @@
         <v>80</v>
       </c>
       <c r="U26" s="3" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="V26" s="3" t="n">
         <v>24.2</v>
@@ -2656,14 +2647,14 @@
       <c r="W26" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="X26" s="8" t="n">
+      <c r="X26" s="3" t="n">
         <v>24.6</v>
       </c>
       <c r="Y26" s="3" t="n">
         <v>81.09999999999999</v>
       </c>
       <c r="Z26" s="3" t="n">
-        <v>17.6</v>
+        <v>7.6</v>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -2679,7 +2670,7 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1354.4</v>
+        <v>354.8</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>2.2</v>
@@ -2691,13 +2682,13 @@
         <v>23.8</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>18.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>17.8</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>2.9</v>
@@ -2715,7 +2706,7 @@
         <v>20.8</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>88.5</v>
+        <v>87.5</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>2.9</v>
@@ -2732,7 +2723,7 @@
       <c r="T27" s="3" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="U27" s="8" t="n">
+      <c r="U27" s="3" t="n">
         <v>10.6</v>
       </c>
       <c r="V27" s="3" t="n">
@@ -2820,7 +2811,7 @@
       <c r="U28" s="3" t="n">
         <v>13.4</v>
       </c>
-      <c r="V28" s="8" t="n">
+      <c r="V28" s="3" t="n">
         <v>26</v>
       </c>
       <c r="W28" s="3" t="n">
@@ -2849,7 +2840,7 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>20.8</v>
+        <v>40.8</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>29.4</v>
@@ -2861,7 +2852,7 @@
         <v>24.9</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>19.1</v>
+        <v>9.1</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>20.1</v>
@@ -2873,7 +2864,7 @@
         <v>2.9</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>10.2</v>
+        <v>0.2</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>20.3</v>
@@ -2881,7 +2872,7 @@
       <c r="M29" s="3" t="n">
         <v>19.2</v>
       </c>
-      <c r="N29" s="8" t="n">
+      <c r="N29" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="O29" s="3" t="n">
@@ -2905,7 +2896,7 @@
       <c r="U29" s="3" t="n">
         <v>14.6</v>
       </c>
-      <c r="V29" s="8" t="n">
+      <c r="V29" s="3" t="n">
         <v>25.5</v>
       </c>
       <c r="W29" s="3" t="n">
@@ -2946,10 +2937,10 @@
         <v>124.1</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>152.5</v>
+        <v>52.5</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>191.7</v>
+        <v>91.3</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>10</v>
@@ -2961,7 +2952,7 @@
         <v>25.4</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>99.59999999999999</v>
+        <v>29.6</v>
       </c>
       <c r="M30" s="3" t="n">
         <v>93.2</v>
@@ -2988,7 +2979,7 @@
         <v>332.8</v>
       </c>
       <c r="U30" s="3" t="n">
-        <v>16.4</v>
+        <v>6.4</v>
       </c>
       <c r="V30" s="3" t="n">
         <v>123.1</v>
@@ -3022,7 +3013,7 @@
         <v>37.1</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>20.1</v>
+        <v>30.1</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>19.6</v>
@@ -3033,20 +3024,20 @@
       <c r="G31" s="3" t="n">
         <v>10.5</v>
       </c>
-      <c r="H31" s="8" t="n">
+      <c r="H31" s="3" t="n">
         <v>18.4</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>13.2</v>
+        <v>3.2</v>
       </c>
       <c r="K31" s="3" t="n">
         <v>0.1</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
       <c r="M31" s="3" t="n">
         <v>18.6</v>
@@ -3066,11 +3057,11 @@
       <c r="R31" s="3" t="n">
         <v>22.7</v>
       </c>
-      <c r="S31" s="8" t="n">
+      <c r="S31" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="T31" s="3" t="n">
-        <v>66</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="U31" s="3" t="n">
         <v>1.2</v>
@@ -3104,25 +3095,25 @@
         </is>
       </c>
       <c r="C32" s="3" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="D32" s="8" t="n">
-        <v>352.8</v>
+        <v>43.7</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>32.8</v>
       </c>
       <c r="E32" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F32" s="8" t="n">
-        <v>66.90000000000001</v>
-      </c>
-      <c r="G32" s="8" t="n">
+      <c r="F32" s="3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="G32" s="3" t="n">
         <v>12.6</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>18.2</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>4.4</v>
@@ -3136,7 +3127,7 @@
       <c r="M32" s="3" t="n">
         <v>19.3</v>
       </c>
-      <c r="N32" s="8" t="n">
+      <c r="N32" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="O32" s="3" t="n">
@@ -3160,17 +3151,17 @@
       <c r="U32" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="V32" s="8" t="n">
+      <c r="V32" s="3" t="n">
         <v>28.2</v>
       </c>
-      <c r="W32" s="8" t="n">
+      <c r="W32" s="3" t="n">
         <v>23.7</v>
       </c>
       <c r="X32" s="3" t="n">
         <v>26.4</v>
       </c>
       <c r="Y32" s="3" t="n">
-        <v>69.09999999999999</v>
+        <v>6.9</v>
       </c>
       <c r="Z32" s="3" t="n">
         <v>11.8</v>
@@ -3189,7 +3180,7 @@
         </is>
       </c>
       <c r="C33" s="3" t="n">
-        <v>397.9</v>
+        <v>397</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>33.7</v>
@@ -3240,12 +3231,12 @@
         <v>23.9</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>147.7</v>
+        <v>47.7</v>
       </c>
       <c r="U33" s="3" t="n">
         <v>2.6</v>
       </c>
-      <c r="V33" s="8" t="n">
+      <c r="V33" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="W33" s="3" t="n">
@@ -3258,7 +3249,7 @@
         <v>77.59999999999999</v>
       </c>
       <c r="Z33" s="3" t="n">
-        <v>17.4</v>
+        <v>7.4</v>
       </c>
       <c r="AA33" s="3" t="inlineStr">
         <is>
@@ -3274,7 +3265,7 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1362.4</v>
+        <v>362.4</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>30.4</v>
@@ -3289,7 +3280,7 @@
         <v>10.2</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>2.2</v>
@@ -3340,7 +3331,7 @@
         <v>27.2</v>
       </c>
       <c r="Y34" s="3" t="n">
-        <v>8.300000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="Z34" s="3" t="n">
         <v>5.4</v>
@@ -3386,13 +3377,13 @@
         <v>9</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M35" s="3" t="n">
         <v>19.3</v>
       </c>
       <c r="N35" s="3" t="n">
-        <v>20</v>
+        <v>21.5</v>
       </c>
       <c r="O35" s="3" t="n">
         <v>85.40000000000001</v>
@@ -3446,7 +3437,7 @@
       <c r="C36" s="3" t="n">
         <v>398.9</v>
       </c>
-      <c r="D36" s="8" t="n">
+      <c r="D36" s="3" t="n">
         <v>28.6</v>
       </c>
       <c r="E36" s="3" t="n">
@@ -3458,7 +3449,7 @@
       <c r="G36" s="3" t="n">
         <v>8.6</v>
       </c>
-      <c r="H36" s="8" t="n">
+      <c r="H36" s="3" t="n">
         <v>19</v>
       </c>
       <c r="I36" s="3" t="n">
@@ -3529,7 +3520,7 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>168.3</v>
+        <v>1683.5</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>150.1</v>
@@ -3541,7 +3532,7 @@
         <v>125.5</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>149.2</v>
+        <v>49.2</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>92.40000000000001</v>
@@ -3553,7 +3544,7 @@
         <v>15.7</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>102.8</v>
+        <v>10.2</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>103.5</v>
@@ -3614,7 +3605,7 @@
         </is>
       </c>
       <c r="C38" s="3" t="n">
-        <v>2326.7</v>
+        <v>336.7</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>30</v>
@@ -3622,7 +3613,7 @@
       <c r="E38" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F38" s="8" t="n">
+      <c r="F38" s="3" t="n">
         <v>25.1</v>
       </c>
       <c r="G38" s="3" t="n">
@@ -3632,19 +3623,19 @@
         <v>18.5</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>2.5</v>
+        <v>22.5</v>
       </c>
       <c r="J38" s="3" t="n">
         <v>3.1</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>20.7</v>
       </c>
       <c r="M38" s="3" t="n">
-        <v>1.9</v>
+        <v>19.3</v>
       </c>
       <c r="N38" s="3" t="n">
         <v>21.4</v>
@@ -3656,7 +3647,7 @@
         <v>3</v>
       </c>
       <c r="Q38" s="3" t="n">
-        <v>27.9</v>
+        <v>27.2</v>
       </c>
       <c r="R38" s="3" t="n">
         <v>23.1</v>
@@ -3668,7 +3659,7 @@
         <v>68.7</v>
       </c>
       <c r="U38" s="3" t="n">
-        <v>13.1</v>
+        <v>18.1</v>
       </c>
       <c r="V38" s="3" t="n">
         <v>25.2</v>
@@ -3699,7 +3690,7 @@
         </is>
       </c>
       <c r="C39" s="3" t="n">
-        <v>1400.8</v>
+        <v>400.8</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>31.8</v>
@@ -3720,7 +3711,7 @@
         <v>2.5</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>13.9</v>
+        <v>3.9</v>
       </c>
       <c r="K39" s="3" t="n">
         <v>0</v>
@@ -3731,7 +3722,7 @@
       <c r="M39" s="3" t="n">
         <v>19.5</v>
       </c>
-      <c r="N39" s="8" t="n">
+      <c r="N39" s="3" t="n">
         <v>22</v>
       </c>
       <c r="O39" s="3" t="n">
@@ -3758,7 +3749,7 @@
       <c r="V39" s="3" t="n">
         <v>26.8</v>
       </c>
-      <c r="W39" s="8" t="n">
+      <c r="W39" s="3" t="n">
         <v>23.8</v>
       </c>
       <c r="X39" s="3" t="n">
@@ -3786,20 +3777,20 @@
       <c r="C40" s="3" t="n">
         <v>74.40000000000001</v>
       </c>
-      <c r="D40" s="8" t="n">
-        <v>84.09999999999999</v>
+      <c r="D40" s="3" t="n">
+        <v>24.1</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>20.2</v>
       </c>
-      <c r="F40" s="8" t="n">
-        <v>22.1</v>
+      <c r="F40" s="3" t="n">
+        <v>222.1</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="H40" s="8" t="n">
-        <v>129</v>
+        <v>3.9</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>19</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.4</v>
@@ -3869,19 +3860,19 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>244.8</v>
+        <v>448.2</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>8.9</v>
+        <v>29.4</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="F41" s="8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="F41" s="3" t="n">
         <v>24.5</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>19.9</v>
+        <v>9.9</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>17.4</v>
@@ -3920,7 +3911,7 @@
         <v>21.7</v>
       </c>
       <c r="T41" s="3" t="n">
-        <v>58.4</v>
+        <v>57.4</v>
       </c>
       <c r="U41" s="3" t="n">
         <v>16.1</v>
@@ -3954,7 +3945,7 @@
         </is>
       </c>
       <c r="C42" s="3" t="n">
-        <v>116.4</v>
+        <v>464.2</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>32.8</v>
@@ -3965,7 +3956,7 @@
       <c r="F42" s="3" t="n">
         <v>24.9</v>
       </c>
-      <c r="G42" s="8" t="n">
+      <c r="G42" s="3" t="n">
         <v>25.8</v>
       </c>
       <c r="H42" s="3" t="n">
@@ -3981,7 +3972,7 @@
         <v>0.2</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>17.8</v>
+        <v>17.2</v>
       </c>
       <c r="M42" s="3" t="n">
         <v>16.1</v>
@@ -4005,7 +3996,7 @@
         <v>22.2</v>
       </c>
       <c r="T42" s="3" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="U42" s="3" t="n">
         <v>22.2</v>
@@ -4039,18 +4030,18 @@
         </is>
       </c>
       <c r="C43" s="3" t="n">
-        <v>2341.3</v>
+        <v>341.3</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>32</v>
       </c>
-      <c r="E43" s="8" t="n">
-        <v>88.59999999999999</v>
+      <c r="E43" s="3" t="n">
+        <v>18.6</v>
       </c>
       <c r="F43" s="3" t="n">
         <v>25.3</v>
       </c>
-      <c r="G43" s="8" t="n">
+      <c r="G43" s="3" t="n">
         <v>13.4</v>
       </c>
       <c r="H43" s="3" t="n">
@@ -4071,14 +4062,14 @@
       <c r="M43" s="3" t="n">
         <v>17.7</v>
       </c>
-      <c r="N43" s="8" t="n">
+      <c r="N43" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="O43" s="3" t="n">
-        <v>188.1</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="P43" s="3" t="n">
-        <v>12.5</v>
+        <v>2.5</v>
       </c>
       <c r="Q43" s="3" t="n">
         <v>24.7</v>
@@ -4086,7 +4077,7 @@
       <c r="R43" s="3" t="n">
         <v>22.3</v>
       </c>
-      <c r="S43" s="8" t="n">
+      <c r="S43" s="3" t="n">
         <v>25.4</v>
       </c>
       <c r="T43" s="3" t="n">
@@ -4108,7 +4099,7 @@
         <v>82.8</v>
       </c>
       <c r="Z43" s="3" t="n">
-        <v>14.6</v>
+        <v>4.6</v>
       </c>
       <c r="AA43" s="3" t="inlineStr">
         <is>
@@ -4132,7 +4123,7 @@
       <c r="E44" s="3" t="n">
         <v>19</v>
       </c>
-      <c r="F44" s="8" t="n">
+      <c r="F44" s="3" t="n">
         <v>21.5</v>
       </c>
       <c r="G44" s="3" t="n">
@@ -4148,16 +4139,16 @@
         <v>0.6</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="L44" s="8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="L44" s="3" t="n">
         <v>19.4</v>
       </c>
       <c r="M44" s="3" t="n">
-        <v>18.2</v>
-      </c>
-      <c r="N44" s="8" t="n">
-        <v>4.1</v>
+        <v>28.2</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>20.1</v>
       </c>
       <c r="O44" s="3" t="n">
         <v>240.1</v>
@@ -4178,9 +4169,9 @@
         <v>81</v>
       </c>
       <c r="U44" s="3" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="V44" s="8" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="V44" s="3" t="n">
         <v>22.3</v>
       </c>
       <c r="W44" s="3" t="n">
@@ -4230,19 +4221,19 @@
         <v>30</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>110.4</v>
+        <v>116.4</v>
       </c>
       <c r="M45" s="3" t="n">
         <v>109.2</v>
       </c>
       <c r="N45" s="3" t="n">
-        <v>1218.1</v>
+        <v>121.1</v>
       </c>
       <c r="O45" s="3" t="n">
         <v>534.4</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>140.4</v>
+        <v>14.2</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>157.5</v>
@@ -4251,23 +4242,23 @@
         <v>129.7</v>
       </c>
       <c r="S45" s="3" t="n">
-        <v>138.5</v>
+        <v>137.5</v>
       </c>
       <c r="T45" s="3" t="n">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="U45" s="3" t="n">
-        <v>1121.5</v>
+        <v>71.5</v>
       </c>
       <c r="V45" s="3" t="n">
         <v>145.5</v>
       </c>
       <c r="W45" s="3" t="n">
-        <v>231.2</v>
+        <v>131.6</v>
       </c>
       <c r="X45" s="3" t="inlineStr"/>
       <c r="Y45" s="3" t="n">
-        <v>48390.4</v>
+        <v>482</v>
       </c>
       <c r="Z45" s="3" t="n">
         <v>5.8</v>
@@ -4292,16 +4283,16 @@
         <v>29</v>
       </c>
       <c r="E46" s="3" t="n">
-        <v>1.8</v>
+        <v>18.2</v>
       </c>
       <c r="F46" s="3" t="n">
         <v>24</v>
       </c>
-      <c r="G46" s="8" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="H46" s="8" t="n">
-        <v>167.6</v>
+      <c r="G46" s="3" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>17.6</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>2.2</v>
@@ -4309,7 +4300,9 @@
       <c r="J46" s="3" t="n">
         <v>2.8</v>
       </c>
-      <c r="K46" s="3" t="inlineStr"/>
+      <c r="K46" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="L46" s="3" t="n">
         <v>19.4</v>
       </c>
@@ -4320,7 +4313,7 @@
         <v>20.2</v>
       </c>
       <c r="O46" s="3" t="n">
-        <v>89.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="P46" s="3" t="n">
         <v>2.4</v>
@@ -4329,7 +4322,7 @@
         <v>26.2</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>21.6</v>
+        <v>221.6</v>
       </c>
       <c r="S46" s="3" t="n">
         <v>22.9</v>
@@ -4343,10 +4336,10 @@
       <c r="V46" s="3" t="n">
         <v>24.2</v>
       </c>
-      <c r="W46" s="8" t="n">
+      <c r="W46" s="3" t="n">
         <v>21.8</v>
       </c>
-      <c r="X46" s="8" t="n">
+      <c r="X46" s="3" t="n">
         <v>24.7</v>
       </c>
       <c r="Y46" s="3" t="inlineStr"/>
